--- a/backend/exports/All_Extracted_Leads.xlsx
+++ b/backend/exports/All_Extracted_Leads.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="__lead_export_mapping__" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LeadCommonImportDTO'!$A$1:$P$329</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LeadCommonImportDTO'!$A$1:$P$331</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -930,13 +930,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P329"/>
+  <dimension ref="A1:P331"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.88671875" defaultRowHeight="12" customHeight="1"/>
   <cols>
     <col width="11.109375" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
     <col width="50" customWidth="1" style="2" min="2" max="2"/>
     <col width="28.44140625" customWidth="1" style="2" min="3" max="3"/>
-    <col width="29.5546875" customWidth="1" style="3" min="4" max="4"/>
+    <col width="50" customWidth="1" style="3" min="4" max="4"/>
     <col width="19" customWidth="1" style="2" min="5" max="5"/>
     <col width="32.44140625" customWidth="1" style="1" min="6" max="6"/>
     <col width="44.5546875" customWidth="1" style="2" min="7" max="7"/>
@@ -10558,9 +10558,6 @@
           <t>MG MEDITECH</t>
         </is>
       </c>
-      <c r="C316" t="inlineStr"/>
-      <c r="D316" t="inlineStr"/>
-      <c r="E316" t="inlineStr"/>
       <c r="F316" t="inlineStr">
         <is>
           <t>078389 48874</t>
@@ -10581,17 +10578,11 @@
           <t>Noida</t>
         </is>
       </c>
-      <c r="J316" t="inlineStr"/>
-      <c r="K316" t="inlineStr"/>
       <c r="L316" t="inlineStr">
         <is>
           <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable; unverified: location could not be confirmed against the requested area</t>
         </is>
       </c>
-      <c r="M316" t="inlineStr"/>
-      <c r="N316" t="inlineStr"/>
-      <c r="O316" t="inlineStr"/>
-      <c r="P316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -10604,9 +10595,6 @@
           <t>Medico Electrode</t>
         </is>
       </c>
-      <c r="C317" t="inlineStr"/>
-      <c r="D317" t="inlineStr"/>
-      <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
         <is>
           <t>0120 488 0600</t>
@@ -10642,10 +10630,6 @@
           <t>unverified: declared industry could not be matched to a target segment; unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M317" t="inlineStr"/>
-      <c r="N317" t="inlineStr"/>
-      <c r="O317" t="inlineStr"/>
-      <c r="P317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -10658,7 +10642,6 @@
           <t>Vignaharta Enterprises Private Limited</t>
         </is>
       </c>
-      <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr">
         <is>
           <t>Saket Agarwal</t>
@@ -10704,10 +10687,6 @@
           <t>unverified: declared industry could not be matched to a target segment; unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M318" t="inlineStr"/>
-      <c r="N318" t="inlineStr"/>
-      <c r="O318" t="inlineStr"/>
-      <c r="P318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -10720,9 +10699,6 @@
           <t>iLife Medical Devices Pvt Ltd, Noida Office</t>
         </is>
       </c>
-      <c r="C319" t="inlineStr"/>
-      <c r="D319" t="inlineStr"/>
-      <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
         <is>
           <t>0120 320 0663</t>
@@ -10743,7 +10719,6 @@
           <t>Noida</t>
         </is>
       </c>
-      <c r="J319" t="inlineStr"/>
       <c r="K319" t="inlineStr">
         <is>
           <t>₹22.75 Crore</t>
@@ -10754,10 +10729,6 @@
           <t>unverified: declared industry could not be matched to a target segment; unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M319" t="inlineStr"/>
-      <c r="N319" t="inlineStr"/>
-      <c r="O319" t="inlineStr"/>
-      <c r="P319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -10770,7 +10741,6 @@
           <t>Divine Health Home Care</t>
         </is>
       </c>
-      <c r="C320" t="inlineStr"/>
       <c r="D320" t="inlineStr">
         <is>
           <t>Moh Irshad</t>
@@ -10801,17 +10771,11 @@
           <t>Noida</t>
         </is>
       </c>
-      <c r="J320" t="inlineStr"/>
-      <c r="K320" t="inlineStr"/>
       <c r="L320" t="inlineStr">
         <is>
           <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M320" t="inlineStr"/>
-      <c r="N320" t="inlineStr"/>
-      <c r="O320" t="inlineStr"/>
-      <c r="P320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -10824,7 +10788,6 @@
           <t>Life Patient Home Care</t>
         </is>
       </c>
-      <c r="C321" t="inlineStr"/>
       <c r="D321" t="inlineStr">
         <is>
           <t>Sameer Ahmed</t>
@@ -10855,17 +10818,11 @@
           <t>Noida</t>
         </is>
       </c>
-      <c r="J321" t="inlineStr"/>
-      <c r="K321" t="inlineStr"/>
       <c r="L321" t="inlineStr">
         <is>
           <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M321" t="inlineStr"/>
-      <c r="N321" t="inlineStr"/>
-      <c r="O321" t="inlineStr"/>
-      <c r="P321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -10878,15 +10835,11 @@
           <t>Coloplast India Pvt. Ltd.</t>
         </is>
       </c>
-      <c r="C322" t="inlineStr"/>
-      <c r="D322" t="inlineStr"/>
-      <c r="E322" t="inlineStr"/>
       <c r="F322" t="inlineStr">
         <is>
           <t>0120 407 1300</t>
         </is>
       </c>
-      <c r="G322" t="inlineStr"/>
       <c r="H322" t="inlineStr">
         <is>
           <t>IGL Complex, 4th Floor (Right Wing), Tower 3, Plot No. – 2B, Sector 126, Noida, Uttar Pradesh 201304</t>
@@ -10912,10 +10865,6 @@
           <t>unverified: declared industry could not be matched to a target segment; unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M322" t="inlineStr"/>
-      <c r="N322" t="inlineStr"/>
-      <c r="O322" t="inlineStr"/>
-      <c r="P322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -10928,9 +10877,6 @@
           <t>JK Engineering Works</t>
         </is>
       </c>
-      <c r="C323" t="inlineStr"/>
-      <c r="D323" t="inlineStr"/>
-      <c r="E323" t="inlineStr"/>
       <c r="F323" t="inlineStr">
         <is>
           <t>082850 26446</t>
@@ -10951,17 +10897,11 @@
           <t>Noida</t>
         </is>
       </c>
-      <c r="J323" t="inlineStr"/>
-      <c r="K323" t="inlineStr"/>
       <c r="L323" t="inlineStr">
         <is>
           <t>unverified: declared industry could not be matched to a target segment; unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M323" t="inlineStr"/>
-      <c r="N323" t="inlineStr"/>
-      <c r="O323" t="inlineStr"/>
-      <c r="P323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -10974,7 +10914,6 @@
           <t>Kuvera Organics Pvt Ltd</t>
         </is>
       </c>
-      <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr">
         <is>
           <t>Mr Atul Kumar Gupta</t>
@@ -10990,7 +10929,6 @@
           <t>098102 28335</t>
         </is>
       </c>
-      <c r="G324" t="inlineStr"/>
       <c r="H324" t="inlineStr">
         <is>
           <t>G-2514, Prateek Edifice, Sector 107,Noida - 201304, Uttar Pradesh, India</t>
@@ -11016,10 +10954,6 @@
           <t>unverified: declared industry could not be matched to a target segment; unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M324" t="inlineStr"/>
-      <c r="N324" t="inlineStr"/>
-      <c r="O324" t="inlineStr"/>
-      <c r="P324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -11032,7 +10966,6 @@
           <t>Innovation Meditech Pvt. Ltd.</t>
         </is>
       </c>
-      <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr">
         <is>
           <t>Rajeev Agarwal</t>
@@ -11078,10 +11011,6 @@
           <t>unverified: declared industry could not be matched to a target segment; unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M325" t="inlineStr"/>
-      <c r="N325" t="inlineStr"/>
-      <c r="O325" t="inlineStr"/>
-      <c r="P325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -11094,9 +11023,6 @@
           <t>SpeechGears</t>
         </is>
       </c>
-      <c r="C326" t="inlineStr"/>
-      <c r="D326" t="inlineStr"/>
-      <c r="E326" t="inlineStr"/>
       <c r="F326" t="inlineStr">
         <is>
           <t>097735 57256</t>
@@ -11132,10 +11058,6 @@
           <t>unverified: declared industry could not be matched to a target segment; unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M326" t="inlineStr"/>
-      <c r="N326" t="inlineStr"/>
-      <c r="O326" t="inlineStr"/>
-      <c r="P326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -11148,9 +11070,6 @@
           <t>MB Plastic Industries</t>
         </is>
       </c>
-      <c r="C327" t="inlineStr"/>
-      <c r="D327" t="inlineStr"/>
-      <c r="E327" t="inlineStr"/>
       <c r="F327" t="inlineStr">
         <is>
           <t>+911204985442</t>
@@ -11186,10 +11105,6 @@
           <t>unverified: declared industry could not be matched to a target segment; unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M327" t="inlineStr"/>
-      <c r="N327" t="inlineStr"/>
-      <c r="O327" t="inlineStr"/>
-      <c r="P327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -11202,7 +11117,6 @@
           <t>OPTIAN HEALTHCARE PVT LTD</t>
         </is>
       </c>
-      <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr">
         <is>
           <t>Reenu Gupta</t>
@@ -11233,7 +11147,6 @@
           <t>Noida</t>
         </is>
       </c>
-      <c r="J328" t="inlineStr"/>
       <c r="K328" t="inlineStr">
         <is>
           <t>₹1.19 Cr</t>
@@ -11244,10 +11157,6 @@
           <t>unverified: declared industry could not be matched to a target segment; unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M328" t="inlineStr"/>
-      <c r="N328" t="inlineStr"/>
-      <c r="O328" t="inlineStr"/>
-      <c r="P328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -11260,9 +11169,6 @@
           <t>AB CONTRACTS</t>
         </is>
       </c>
-      <c r="C329" t="inlineStr"/>
-      <c r="D329" t="inlineStr"/>
-      <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr">
         <is>
           <t>011-46710423</t>
@@ -11283,20 +11189,113 @@
           <t>Noida</t>
         </is>
       </c>
-      <c r="J329" t="inlineStr"/>
-      <c r="K329" t="inlineStr"/>
       <c r="L329" t="inlineStr">
         <is>
           <t>unverified: turnover unavailable; unverified: employee count unavailable</t>
         </is>
       </c>
-      <c r="M329" t="inlineStr"/>
-      <c r="N329" t="inlineStr"/>
-      <c r="O329" t="inlineStr"/>
-      <c r="P329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Speedtec - Manufacturer of Centrifugal Pumps &amp; Water Pumps</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>+914222570345</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>speedpumps@gmail.com</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>12/1, Jothi Nagar 2nd Street, Ramanuja Nagar, Near Hope College, Coimbatore - 641 015</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>33AHWPK2133M1Z1</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Rs. 40 lakhs to 1.5 Cr.</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>unverified: employee count unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Goodbooks</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>The Hindusthan Engineering Industries</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>{'name': 'Centrifugal Self-Priming High', 'source_url': 'https://www.theipumps.in/', 'designation': 'Head'}</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>+919363146829</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>hindustanengineeringindustry@gmail.com</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>Ramanathapuram,, Coimbatore, Tamil Nadu – 641036</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>33AAKFT0008R1ZZ</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>₹2,999.49 Crore</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>unverified: employee count unavailable</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P329"/>
+  <autoFilter ref="A1:P331"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
 </worksheet>
